--- a/Luban/Config/Datas/__beans__.xlsx
+++ b/Luban/Config/Datas/__beans__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace2\luban_examples\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52892A95-BBDD-42B6-A9C8-E869A5FA9CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EDE883C-4E16-4BE9-B50A-E33D29CCCA46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5880" yWindow="3705" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="68">
   <si>
     <t>##var</t>
   </si>
@@ -92,6 +92,186 @@
   </si>
   <si>
     <t>字段变体</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>交互物品ID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>InteractionItemID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>位置X</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>位置Y</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneInteractionItemData</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>##</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Position</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>X</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>位置</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>地板坐标</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>X1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>X2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneFloorPosition</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景交互物品数据</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScenePassageData</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景通道数据</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PassageID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeatherPoolInGroupData</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>天气组中的天气池子数据</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SeasonID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>季候ID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeatherGroupID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>天气池ID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeatherPoolData</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>天气池数据</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeatherType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>天气类型</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>权重</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MinContinue</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxContinue</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>最小持续时间</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大持续时间</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weight</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PasserbyInSceneData</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>路人所在场景数据</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TimePeriod</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>路人表时间段(参数格式为-1|x（每日|概率百分比）或日期类型id|x（指定类型的日期|概率百分比），可同时存在多个参数，逗号相隔，仅从满足的中选概率最高的进行触发判定)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Type</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Probability</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -99,7 +279,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -130,11 +310,22 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -181,13 +372,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -467,112 +658,384 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Q26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="4" width="20.625" customWidth="1"/>
-    <col min="5" max="6" width="12.25" customWidth="1"/>
-    <col min="7" max="9" width="15" customWidth="1"/>
-    <col min="10" max="12" width="13.5" customWidth="1"/>
-    <col min="13" max="13" width="10.375" customWidth="1"/>
+    <col min="1" max="1" width="9" style="2"/>
+    <col min="2" max="3" width="30.125" style="2" customWidth="1"/>
+    <col min="4" max="5" width="20.625" style="2" customWidth="1"/>
+    <col min="6" max="7" width="12.25" style="2" customWidth="1"/>
+    <col min="8" max="10" width="15" style="2" customWidth="1"/>
+    <col min="11" max="11" width="18.375" style="2" customWidth="1"/>
+    <col min="12" max="13" width="13.5" style="2" customWidth="1"/>
+    <col min="14" max="14" width="10.375" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3"/>
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q1" s="3"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="Q3" s="2" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="K15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K17" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K19" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K21" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B22" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K24" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B25" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K26" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="J1:P1"/>
+    <mergeCell ref="K1:Q1"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Luban/Config/Datas/__beans__.xlsx
+++ b/Luban/Config/Datas/__beans__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EDE883C-4E16-4BE9-B50A-E33D29CCCA46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D70B3402-4C83-45DB-A717-F8E7E8ED6DC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5880" yWindow="3705" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="71">
   <si>
     <t>##var</t>
   </si>
@@ -199,10 +199,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>WeatherGroupID</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>天气池ID</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -215,14 +211,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>WeatherType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>天气类型</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>权重</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -272,6 +260,30 @@
   </si>
   <si>
     <t>Probability</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeatherPoolID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeatherID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>天气类ID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>类型</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景ID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>概率</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -922,77 +934,80 @@
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K17" s="2" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="M17" s="2" t="s">
         <v>23</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="K18" s="2" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="M18" s="2" t="s">
         <v>23</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K19" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="M19" s="2" t="s">
         <v>23</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K20" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>23</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K21" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>23</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>23</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.2">
@@ -1013,24 +1028,30 @@
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="O25" s="2" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.2">
       <c r="K26" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="M26" s="2" t="s">
         <v>26</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Config/Datas/__beans__.xlsx
+++ b/Luban/Config/Datas/__beans__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D70B3402-4C83-45DB-A717-F8E7E8ED6DC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1152562-6A90-442F-9602-A13D21149556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="76">
   <si>
     <t>##var</t>
   </si>
@@ -284,6 +284,26 @@
   </si>
   <si>
     <t>概率</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CommonPoolData</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>池子东西ID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Num</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>池子东西数量</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -670,7 +690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -1054,6 +1074,39 @@
         <v>70</v>
       </c>
     </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B27" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K28" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K29" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="K1:Q1"/>

--- a/Luban/Config/Datas/__beans__.xlsx
+++ b/Luban/Config/Datas/__beans__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1152562-6A90-442F-9602-A13D21149556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA2D451F-A70F-4DA8-B965-1E515D879CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
